--- a/gibbs_EASG690_HW3/homework3Part3/Rader_min_plant_data.xlsx
+++ b/gibbs_EASG690_HW3/homework3Part3/Rader_min_plant_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/barrettgibbs/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/barrettgibbs/Desktop/easg_Data_Analysis/gibbs_EASG690_HW3/homework3Part3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D6CED49-B338-BB44-A901-81F8257C868E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31D14883-3C90-A84F-8D41-0EC056C885E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1400" yWindow="760" windowWidth="28000" windowHeight="17240" xr2:uid="{A1843538-1F98-7848-BEDC-12AD6ABCB7CB}"/>
   </bookViews>
